--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf4f5f0bfc6644808"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3806b19b3ad477a"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R5f889bfc37dc40bf"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re6e39221cd584040"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb3806b19b3ad477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R84bcd486e6ce4346"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Re6e39221cd584040"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R764b0147fa4344b2"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R84bcd486e6ce4346"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re57e2a8478b84c74"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R764b0147fa4344b2"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R56d3586066754225"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re57e2a8478b84c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38cde63260c5403e"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R56d3586066754225"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1e9ada7105a7442b"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38cde63260c5403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ab54e1550c14e48"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1e9ada7105a7442b"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0a3e0c0338f644ed"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ab54e1550c14e48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb54c85530fa54817"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R0a3e0c0338f644ed"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R2b11d02cda344f7a"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb54c85530fa54817"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c8b1e94efaf4ec2"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R2b11d02cda344f7a"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R999958d656054094"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c8b1e94efaf4ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72dce19d266d4159"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R999958d656054094"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R3dd4a2f7406047cb"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R72dce19d266d4159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc45c888b44dc416f"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R3dd4a2f7406047cb"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1aa91c9e2ac24f86"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc45c888b44dc416f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf3d755c144684967"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1aa91c9e2ac24f86"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R8d5883761aec4bef"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf3d755c144684967"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3776faf9ac754a7d"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R8d5883761aec4bef"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc6c680d02c9f490a"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3776faf9ac754a7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3ad65409dbb4a81"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc6c680d02c9f490a"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R4080437352644c12"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc3ad65409dbb4a81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdcc6dfe01f8f46c2"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R4080437352644c12"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R7a685b1f152f44b7"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdcc6dfe01f8f46c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9d18410fb02f4885"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R7a685b1f152f44b7"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R103a94ae30c44c6a"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
